--- a/public/sample-documents/Quarters_Sample.xlsx
+++ b/public/sample-documents/Quarters_Sample.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SENARAI_KUARTERS" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="SENARAI_KUARTERS" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -49,11 +46,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -421,42 +415,34 @@
   </sheetPr>
   <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="11" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>KATEGORI / KAWASAN</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>ALAMAT KUARTERS</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>SEWA (RM)</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>SENGGARA (RM)</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>PENALTI (RM)</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>NO. RUMAH / NO. UNIT</t>
         </is>
@@ -465,182 +451,224 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>Kategori C</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Blok K01, Jalan Kebudayaan 1, 81300 Johor Bahru, Johor</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>450</v>
-      </c>
-      <c r="D2" t="n">
-        <v>50</v>
-      </c>
-      <c r="E2" t="n">
-        <v>0</v>
+          <t>Blok C1, Alamat Kuarters C</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>450</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>JB-K01-A-01</t>
+          <t>UNIT-C01</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>Kategori C</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Blok K01, Jalan Kebudayaan 1, 81300 Johor Bahru, Johor</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>450</v>
-      </c>
-      <c r="D3" t="n">
-        <v>50</v>
-      </c>
-      <c r="E3" t="n">
-        <v>0</v>
+          <t>Blok C1, Alamat Kuarters C</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>450</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>JB-K01-A-02</t>
+          <t>UNIT-C02</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>Kategori C</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Blok K01, Jalan Kebudayaan 1, 81300 Johor Bahru, Johor</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>450</v>
-      </c>
-      <c r="D4" t="n">
-        <v>50</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0</v>
+          <t>Blok C1, Alamat Kuarters C</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>450</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>JB-K01-A-03</t>
+          <t>UNIT-C03</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>Kategori F</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Blok F02, Jalan Pendidikan 2, 81300 Johor Bahru, Johor</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>320</v>
-      </c>
-      <c r="D5" t="n">
-        <v>30</v>
-      </c>
-      <c r="E5" t="n">
-        <v>10</v>
+          <t>Blok F1, Alamat Kuarters F</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>320</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>JB-F02-01</t>
+          <t>UNIT-F01</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>Kategori F</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Blok F02, Jalan Pendidikan 2, 81300 Johor Bahru, Johor</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>320</v>
-      </c>
-      <c r="D6" t="n">
-        <v>30</v>
-      </c>
-      <c r="E6" t="n">
-        <v>10</v>
+          <t>Blok F1, Alamat Kuarters F</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>320</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>JB-F02-02</t>
+          <t>UNIT-F02</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>Kategori E</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Blok E03, Jalan Teknologi 3, 81300 Johor Bahru, Johor</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>150</v>
-      </c>
-      <c r="D7" t="n">
-        <v>20</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0</v>
+          <t>Blok E1, Alamat Kuarters E</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>JB-E03-01</t>
+          <t>UNIT-E01</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>Kategori G</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Blok G04, Jalan Inovasi 4, 81300 Johor Bahru, Johor</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>120</v>
-      </c>
-      <c r="D8" t="n">
-        <v>15</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0</v>
+          <t>Blok G1, Alamat Kuarters G</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>JB-G04-01</t>
+          <t>UNIT-G01</t>
         </is>
       </c>
     </row>
